--- a/output/法令更新監視台帳_20260316.xlsx
+++ b/output/法令更新監視台帳_20260316.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t.namigata\Desktop\python_practice\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDF5698-F9BC-4E94-8A99-CED7F27D1678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -190,12 +196,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -203,8 +209,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -250,17 +263,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -298,7 +319,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -332,6 +353,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -366,9 +388,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -541,11 +564,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="70.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,7 +588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -573,7 +602,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -587,7 +616,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -601,7 +630,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -615,7 +644,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -629,7 +658,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -643,7 +672,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -657,7 +686,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -671,7 +700,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -685,7 +714,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -699,7 +728,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -713,7 +742,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -727,7 +756,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -741,7 +770,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -755,7 +784,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -769,7 +798,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -783,7 +812,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -797,7 +826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -811,7 +840,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -825,7 +854,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -839,7 +868,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -853,7 +882,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -867,7 +896,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -881,7 +910,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -895,7 +924,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -909,7 +938,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -923,7 +952,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -937,7 +966,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -951,7 +980,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -965,7 +994,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -979,7 +1008,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -994,6 +1023,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>